--- a/artfynd/A 33395-2026 artfynd.xlsx
+++ b/artfynd/A 33395-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136309473</v>
       </c>
       <c r="B2" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136309474</v>
       </c>
       <c r="B3" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136309469</v>
       </c>
       <c r="B4" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136309467</v>
       </c>
       <c r="B5" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136309466</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136309471</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136309472</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136309477</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136309468</v>
       </c>
       <c r="B10" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136309465</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>136309476</v>
       </c>
       <c r="B12" t="n">
-        <v>78458</v>
+        <v>78459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
